--- a/backend/src/evolve/Kelsic_Data_foldy/Round_1_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_1_top_variants.xlsx
@@ -443,121 +443,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T12N</t>
+          <t>V53R</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9835</v>
+        <v>0.2431666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D5V</t>
+          <t>M21H</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.0095</v>
+        <v>0.9984999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G29N</t>
+          <t>T54S</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9768333333333334</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G29S</t>
+          <t>A34G</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9984999999999999</v>
+        <v>1.01275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L14Q</t>
+          <t>L17F</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.968</v>
+        <v>0.9704999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D5S</t>
+          <t>L26I</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.023666666666667</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P18R</t>
+          <t>V53C</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9165000000000001</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E56A</t>
+          <t>D61E</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.987</v>
+        <v>0.8745000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D5A</t>
+          <t>T12E</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9907499999999999</v>
+        <v>0.9864999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D5I</t>
+          <t>L14S</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.049</v>
+        <v>0.9601666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G29D</t>
+          <t>V32M</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.994</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V55L</t>
+          <t>M21N</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9579999999999999</v>
+        <v>1.013</v>
       </c>
     </row>
   </sheetData>

--- a/backend/src/evolve/Kelsic_Data_foldy/Round_1_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_1_top_variants.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,121 +443,991 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V53R</t>
+          <t>L14M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2431666666666667</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M21H</t>
+          <t>I7M</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T54S</t>
+          <t>V53N</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9768333333333334</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A34G</t>
+          <t>I36M</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.01275</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L17F</t>
+          <t>V32M</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9704999999999999</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L26I</t>
+          <t>V53T</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.699</v>
+        <v>0.9489999999999998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V53C</t>
+          <t>M21F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.949</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D61E</t>
+          <t>T16S</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.9683333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T12E</t>
+          <t>V53R</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9864999999999999</v>
+        <v>0.2431666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L14S</t>
+          <t>V32T</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9601666666666667</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V32M</t>
+          <t>V53P</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.988</v>
+        <v>0.47475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>I7V</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8414999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I7L</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9545</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T54S</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9768333333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T54A</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9934999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>V53H</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L17F</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9704999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T33S</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V53C</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.949</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E25D</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9824999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V53E</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.1835</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T12Q</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9724999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S71L</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9888333333333333</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>V31L</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9973333333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T33Q</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.0045</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q10S</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.9026666666666666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P59Q</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.971</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T54N</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T12M</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L57I</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.9383333333333335</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>M21A</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.98625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>V53D</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>R46K</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.893</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>I47V</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.94975</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H30T</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.9844999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>V53K</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T33H</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P59G</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.9455</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T33M</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>R23Q</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.9964999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>V53Q</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.1515</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>H30N</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.9855</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>I36V</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.0025</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S71T</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.9892500000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>V31M</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F22Y</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T33N</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.0095</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T16N</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.0095</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P59N</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.9430000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>V32L</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.013666666666667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P59K</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.931</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>D5E</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1.029</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>M21T</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P59M</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.977</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>M21S</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.9958333333333332</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>L17M</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L26M</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.826</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>M21N</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B59" t="n">
         <v>1.013</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Q10A</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.7132499999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>D5V</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.0095</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T54G</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.8985000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T12L</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.9253333333333332</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L48M</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.959</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>I7F</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.0245</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P59A</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.9742500000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P18Q</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S71G</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.9957499999999999</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>S71P</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.9542499999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T49M</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.969</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T12N</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.9835</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>R23T</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>H35N</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.987</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L26C</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.7504999999999999</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>V32A</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>M21I</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>S71M</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P18K</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.973</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>M21W</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T54D</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.9390000000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P59L</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.9576666666666668</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>T49N</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>N19S</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.9956666666666666</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L62I</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.9726666666666667</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T12H</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>D5T</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L62M</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Q10N</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T54M</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>N6Q</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1.0045</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>M21Q</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T54Q</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.964</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L17K</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1.034</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>V31A</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1.01325</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>E27Q</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.8260000000000001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P59T</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.9650000000000001</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L26T</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.6545000000000001</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S63M</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.794</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>S71I</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.9783333333333334</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>V53I</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.904</v>
       </c>
     </row>
   </sheetData>
